--- a/data/nfm_hyungbae.xlsx
+++ b/data/nfm_hyungbae.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>seq</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>image_urls</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -516,7 +521,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8271936.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8271936.do</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -527,6 +532,11 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>PS0100200100100508000000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8271936.do</t>
         </is>
       </c>
     </row>
@@ -558,7 +568,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>가로 : 20 세로 : 21.5</t>
+          <t>세로 : 21.5 가로 : 20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -573,7 +583,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8271947.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8271947.do</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -584,6 +594,11 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>PS0100200100100508100000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8271947.do</t>
         </is>
       </c>
     </row>
@@ -630,7 +645,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8338170.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8338170.do</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -641,6 +656,11 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>PS0100200100102918400000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8338170.do</t>
         </is>
       </c>
     </row>
@@ -687,7 +707,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8286812.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8286812.do</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -698,6 +718,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>PS0100200100900091500000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8286812.do</t>
         </is>
       </c>
     </row>
@@ -744,7 +769,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8402624.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8402624.do</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -755,6 +780,11 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>PS0100200100900091400000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8402624.do</t>
         </is>
       </c>
     </row>
@@ -786,7 +816,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>세로 : 34 가로 : 34</t>
+          <t>가로 : 34 세로 : 34</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -801,7 +831,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8292438.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8292438.do</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -812,6 +842,11 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>PS0100200100900091600000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8292438.do</t>
         </is>
       </c>
     </row>
@@ -843,7 +878,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>세로 : 36.5 가로 : 35.5</t>
+          <t>가로 : 35.5 세로 : 36.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -858,7 +893,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8402521.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8402521.do</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -869,6 +904,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>PS0100200100900091700000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8402521.do</t>
         </is>
       </c>
     </row>
@@ -915,7 +955,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8485330.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8485330.do</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -926,6 +966,11 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>PS0100200100109591700000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8485330.do; https://www.nfm.go.kr/common/apiimage/relic/8485331.do</t>
         </is>
       </c>
     </row>
@@ -957,7 +1002,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>세로 : 22.8 가로 : 21.6</t>
+          <t>가로 : 21.6 세로 : 22.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -972,7 +1017,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8485339.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8485338.do</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -983,6 +1028,11 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>PS0100200100109591800000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8485338.do; https://www.nfm.go.kr/common/apiimage/relic/8485339.do</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1064,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>세로 : 19.2 가로 : 17.5</t>
+          <t>가로 : 17.5 세로 : 19.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1029,7 +1079,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8273809.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273809.do</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1040,6 +1090,11 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>PS0100200100100102600000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273809.do; https://www.nfm.go.kr/common/apiimage/relic/8273808.do; https://www.nfm.go.kr/common/apiimage/relic/8273807.do; https://www.nfm.go.kr/common/apiimage/relic/8273810.do; https://www.nfm.go.kr/common/apiimage/relic/8273811.do</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1141,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8269352.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8269349.do</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1097,6 +1152,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>PS0100200100100193500000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8269349.do; https://www.nfm.go.kr/common/apiimage/relic/8269350.do; https://www.nfm.go.kr/common/apiimage/relic/8269352.do; https://www.nfm.go.kr/common/apiimage/relic/8269351.do; https://www.nfm.go.kr/common/apiimage/relic/8269353.do</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1188,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>가로 : 16.2 세로 : 17</t>
+          <t>세로 : 17 가로 : 16.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1143,7 +1203,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8536053.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8536053.do</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1154,6 +1214,11 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>PS0100200100100203300000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8536053.do</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8273837.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273837.do</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1211,6 +1276,11 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>PS0100200100100206600000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273837.do</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1312,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>세로 : 25 가로 : 24</t>
+          <t>가로 : 24 세로 : 25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1257,7 +1327,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8557604.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8557604.do</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1268,6 +1338,11 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>PS0100200100100208200000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8557604.do</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1389,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8299462.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8299462.do</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1325,6 +1400,11 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>PS0100200100100420500000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8299462.do</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1436,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>세로 : 19.7 가로 : 17.5</t>
+          <t>가로 : 17.5 세로 : 19.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1371,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8239576.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8239575.do</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1382,6 +1462,11 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>PS0100200100106377900000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8239575.do; https://www.nfm.go.kr/common/apiimage/relic/8239576.do</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1498,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>길이 : 37 너비 : 38</t>
+          <t>너비 : 38 길이 : 37</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1428,7 +1513,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8565938.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8565938.do</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1439,6 +1524,11 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>PS0100200100107750400000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8565938.do</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1560,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>세로 : 22.5 가로 : 20.3</t>
+          <t>가로 : 20.3 세로 : 22.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1485,7 +1575,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8244369.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8244369.do</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1496,6 +1586,11 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>PS0100200100100420400000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8244369.do</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1637,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8407629.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8407629.do</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1553,6 +1648,11 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>PS0100200100102957600000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8407629.do</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1699,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8288762.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8288762.do</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1610,6 +1710,11 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>PS0100200100900062800000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8288762.do; https://www.nfm.go.kr/common/apiimage/relic/8288763.do</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8559502.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8559501.do</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1667,6 +1772,11 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>PS0100200100900063100000</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8559501.do; https://www.nfm.go.kr/common/apiimage/relic/8559504.do; https://www.nfm.go.kr/common/apiimage/relic/8559503.do; https://www.nfm.go.kr/common/apiimage/relic/8559502.do</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1823,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8412016.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8412016.do</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1724,6 +1834,11 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>PS0100200100107738400000</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8412016.do</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1870,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>가로 : 17 세로 : 18</t>
+          <t>세로 : 18 가로 : 17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1770,7 +1885,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apithumb/relic/8335546.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8335546.do</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1781,6 +1896,11 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>PS0100200100102957500000</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8335546.do</t>
         </is>
       </c>
     </row>

--- a/data/nfm_hyungbae.xlsx
+++ b/data/nfm_hyungbae.xlsx
@@ -630,7 +630,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>세로 : 20.7 가로 : 20.6</t>
+          <t>가로 : 20.6 세로 : 20.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>가로 : 21.6 세로 : 22.8</t>
+          <t>세로 : 22.8 가로 : 21.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273809.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273811.do</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8273809.do; https://www.nfm.go.kr/common/apiimage/relic/8273808.do; https://www.nfm.go.kr/common/apiimage/relic/8273807.do; https://www.nfm.go.kr/common/apiimage/relic/8273810.do; https://www.nfm.go.kr/common/apiimage/relic/8273811.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8273811.do; https://www.nfm.go.kr/common/apiimage/relic/8273807.do; https://www.nfm.go.kr/common/apiimage/relic/8273808.do; https://www.nfm.go.kr/common/apiimage/relic/8273809.do; https://www.nfm.go.kr/common/apiimage/relic/8273810.do</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8269349.do; https://www.nfm.go.kr/common/apiimage/relic/8269350.do; https://www.nfm.go.kr/common/apiimage/relic/8269352.do; https://www.nfm.go.kr/common/apiimage/relic/8269351.do; https://www.nfm.go.kr/common/apiimage/relic/8269353.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8269349.do; https://www.nfm.go.kr/common/apiimage/relic/8269352.do; https://www.nfm.go.kr/common/apiimage/relic/8269351.do; https://www.nfm.go.kr/common/apiimage/relic/8269350.do; https://www.nfm.go.kr/common/apiimage/relic/8269353.do</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>가로 : 24 세로 : 25</t>
+          <t>세로 : 25 가로 : 24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>가로 : 17.5 세로 : 19</t>
+          <t>세로 : 19 가로 : 17.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>가로 : 17.5 세로 : 19.7</t>
+          <t>세로 : 19.7 가로 : 17.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8239575.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8239576.do</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8239575.do; https://www.nfm.go.kr/common/apiimage/relic/8239576.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8239576.do; https://www.nfm.go.kr/common/apiimage/relic/8239575.do</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>의-의류-부분품-보/흉배 / 사회생활-의례생활-상장</t>
+          <t>사회생활-의례생활-상장 / 의-의류-부분품-보/흉배</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>너비 : 38 길이 : 37</t>
+          <t>길이 : 37 너비 : 38</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>가로 : 17.2 세로 : 18</t>
+          <t>세로 : 18 가로 : 17.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>세로 : 59 가로 : 59</t>
+          <t>가로 : 59 세로 : 59</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8559501.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8559502.do</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.nfm.go.kr/common/apiimage/relic/8559501.do; https://www.nfm.go.kr/common/apiimage/relic/8559504.do; https://www.nfm.go.kr/common/apiimage/relic/8559503.do; https://www.nfm.go.kr/common/apiimage/relic/8559502.do</t>
+          <t>https://www.nfm.go.kr/common/apiimage/relic/8559502.do; https://www.nfm.go.kr/common/apiimage/relic/8559501.do; https://www.nfm.go.kr/common/apiimage/relic/8559503.do; https://www.nfm.go.kr/common/apiimage/relic/8559504.do</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>길이 : 430 너비 : 104</t>
+          <t>너비 : 104 길이 : 430</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
